--- a/static/cardapio.xlsx
+++ b/static/cardapio.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daniel\Desktop\America lanche\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daniel\Desktop\America lanche\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -789,7 +789,7 @@
         <v>25</v>
       </c>
       <c r="D5" s="5">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>1</v>
@@ -1086,7 +1086,7 @@
         <v>32</v>
       </c>
       <c r="D40" s="5">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E40" s="5" t="s">
         <v>16</v>
@@ -1124,7 +1124,7 @@
         <v>58</v>
       </c>
       <c r="D43" s="5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E43" s="5"/>
     </row>
@@ -1134,7 +1134,7 @@
         <v>59</v>
       </c>
       <c r="D44" s="5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E44" s="5"/>
     </row>
@@ -1144,7 +1144,7 @@
         <v>60</v>
       </c>
       <c r="D45" s="5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E45" s="5"/>
     </row>
@@ -1154,7 +1154,7 @@
         <v>61</v>
       </c>
       <c r="D46" s="5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E46" s="5"/>
     </row>
@@ -1174,7 +1174,7 @@
         <v>63</v>
       </c>
       <c r="D48" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E48" s="5"/>
     </row>
@@ -1184,7 +1184,7 @@
         <v>64</v>
       </c>
       <c r="D49" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E49" s="5"/>
     </row>
@@ -1214,7 +1214,7 @@
         <v>66</v>
       </c>
       <c r="D52" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E52" s="5"/>
     </row>
@@ -1246,7 +1246,7 @@
         <v>28</v>
       </c>
       <c r="D57" s="5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E57" s="5"/>
     </row>
@@ -1256,7 +1256,7 @@
         <v>27</v>
       </c>
       <c r="D58" s="5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E58" s="5"/>
     </row>
@@ -1276,7 +1276,7 @@
         <v>68</v>
       </c>
       <c r="D60" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E60" s="5"/>
     </row>
@@ -1286,7 +1286,7 @@
         <v>69</v>
       </c>
       <c r="D61" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E61" s="5"/>
     </row>
@@ -1296,7 +1296,7 @@
         <v>70</v>
       </c>
       <c r="D62" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E62" s="5"/>
     </row>
@@ -1328,7 +1328,7 @@
         <v>73</v>
       </c>
       <c r="D67" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E67" s="5"/>
     </row>
@@ -1338,7 +1338,7 @@
         <v>74</v>
       </c>
       <c r="D68" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E68" s="5"/>
     </row>
@@ -1388,7 +1388,7 @@
         <v>79</v>
       </c>
       <c r="D73" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E73" s="5"/>
     </row>
@@ -1398,7 +1398,7 @@
         <v>80</v>
       </c>
       <c r="D74" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E74" s="5"/>
     </row>
